--- a/skills/skill-test/example/no-invented-pv-only.xlsx
+++ b/skills/skill-test/example/no-invented-pv-only.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>States eye_color is not a supported field/PV; does not invent.</t>
+          <t>Pass if the response states that eye_color is not a harmonized subject field and/or is not defined in bundled subject PV metadata. It may present metadata.unharmonized.eye_color=blue (GET or curl) as the unharmonized API filter shape, including case-sensitivity or node-variation caveats. Fail only if it claims eye_color/blue is a validated harmonized controlled subject field or PV, or presents a bare harmonized filter like ?eye_color=blue as supported.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
